--- a/StructureDefinition-ophthalmic-medication-administration.xlsx
+++ b/StructureDefinition-ophthalmic-medication-administration.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.0</t>
+    <t>0.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T17:43:23+00:00</t>
+    <t>2026-09-11T00:16:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ophthalmic-medication-administration.xlsx
+++ b/StructureDefinition-ophthalmic-medication-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T00:16:12+00:00</t>
+    <t>2026-10-19T22:17:00-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1597,17 +1597,17 @@
   <dimension ref="A1:AO52"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="57.265625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="46.94140625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="58.58203125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="48.20703125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.77734375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.8125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.29296875" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.21484375" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.55078125" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.1171875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="10.75390625" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="78.85546875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="83.69140625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1616,27 +1616,27 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="106.67578125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="54.921875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="39.109375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="7.93359375" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.08984375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="14.4296875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="15.31640625" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="108.41015625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="57.66796875" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.10546875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="17.6953125" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="35.90625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="13.44140625" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="11.03515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="40.7734375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="8.51953125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="8.859375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="245.42578125" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="86.66796875" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="19.29296875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="23.9609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="248.7734375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="29.45703125" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="88.21484375" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="18.171875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/StructureDefinition-ophthalmic-medication-administration.xlsx
+++ b/StructureDefinition-ophthalmic-medication-administration.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$48</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1947" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1796" uniqueCount="385">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T22:17:00-03:00</t>
+    <t>2026-10-20T20:13:11-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,9 +87,9 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Records the administration of a medication during an ophthalmic procedure,
-most notably an intravitreal injection. Always linked back to the specific procedure it was
-administered during, via partOf, consistent with FHIR's standard 'larger event of which
+    <t>Records the administration of a medication during an ophthalmic procedure,
+most notably an intravitreal injection. Always linked back to the specific procedure it was
+administered during, via partOf, consistent with FHIR's standard 'larger event of which
 this is a component' pattern.</t>
   </si>
   <si>
@@ -979,6 +979,94 @@
   </si>
   <si>
     <t>MedicationAdministration.dosage.extension</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>MedicationAdministration.dosage.extension:bodySiteEye</t>
+  </si>
+  <si>
+    <t>bodySiteEye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {bodySite|5.3.0}
+</t>
+  </si>
+  <si>
+    <t>Laterality of the administration site, via BodyStructure</t>
+  </si>
+  <si>
+    <t>Record details about the anatomical location of a specimen or body part. This resource may be used when a coded concept does not provide the necessary detail needed for the use case.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>MedicationAdministration.dosage.extension:bodySiteEye.id</t>
+  </si>
+  <si>
+    <t>MedicationAdministration.dosage.extension.id</t>
+  </si>
+  <si>
+    <t>MedicationAdministration.dosage.extension:bodySiteEye.extension</t>
+  </si>
+  <si>
+    <t>MedicationAdministration.dosage.extension.extension</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>MedicationAdministration.dosage.extension:bodySiteEye.url</t>
+  </si>
+  <si>
+    <t>MedicationAdministration.dosage.extension.url</t>
+  </si>
+  <si>
+    <t>identifies the meaning of the extension</t>
+  </si>
+  <si>
+    <t>Source of the definition for the extension code - a logical name or a URL.</t>
+  </si>
+  <si>
+    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/StructureDefinition/bodySite</t>
+  </si>
+  <si>
+    <t>Extension.url</t>
+  </si>
+  <si>
+    <t>MedicationAdministration.dosage.extension:bodySiteEye.value[x]</t>
+  </si>
+  <si>
+    <t>MedicationAdministration.dosage.extension.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://YasniiSS.github.io/fhir4eyes/StructureDefinition/ocular-body-structure)
+</t>
+  </si>
+  <si>
+    <t>Value of extension</t>
+  </si>
+  <si>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
+  </si>
+  <si>
+    <t>Extension.value[x]</t>
   </si>
   <si>
     <t>MedicationAdministration.dosage.modifierExtension</t>
@@ -1020,148 +1108,6 @@
   </si>
   <si>
     <t>RXR-2 Administration Site / RXR-6 Administration Site Modifier</t>
-  </si>
-  <si>
-    <t>MedicationAdministration.dosage.site.id</t>
-  </si>
-  <si>
-    <t>MedicationAdministration.dosage.site.extension</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>MedicationAdministration.dosage.site.extension:bodySiteEye</t>
-  </si>
-  <si>
-    <t>bodySiteEye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {bodySite}
-</t>
-  </si>
-  <si>
-    <t>Laterality of the administration site, via BodyStructure</t>
-  </si>
-  <si>
-    <t>Record details about the anatomical location of a specimen or body part. This resource may be used when a coded concept does not provide the necessary detail needed for the use case.</t>
-  </si>
-  <si>
-    <t>MedicationAdministration.dosage.site.extension:bodySiteEye.id</t>
-  </si>
-  <si>
-    <t>MedicationAdministration.dosage.site.extension.id</t>
-  </si>
-  <si>
-    <t>MedicationAdministration.dosage.site.extension:bodySiteEye.extension</t>
-  </si>
-  <si>
-    <t>MedicationAdministration.dosage.site.extension.extension</t>
-  </si>
-  <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
-  </si>
-  <si>
-    <t>MedicationAdministration.dosage.site.extension:bodySiteEye.url</t>
-  </si>
-  <si>
-    <t>MedicationAdministration.dosage.site.extension.url</t>
-  </si>
-  <si>
-    <t>identifies the meaning of the extension</t>
-  </si>
-  <si>
-    <t>Source of the definition for the extension code - a logical name or a URL.</t>
-  </si>
-  <si>
-    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/StructureDefinition/bodySite</t>
-  </si>
-  <si>
-    <t>Extension.url</t>
-  </si>
-  <si>
-    <t>MedicationAdministration.dosage.site.extension:bodySiteEye.value[x]</t>
-  </si>
-  <si>
-    <t>MedicationAdministration.dosage.site.extension.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://YasniiSS.github.io/fhir4eyes/StructureDefinition/ocular-body-structure)
-</t>
-  </si>
-  <si>
-    <t>Value of extension</t>
-  </si>
-  <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
-  </si>
-  <si>
-    <t>Extension.value[x]</t>
-  </si>
-  <si>
-    <t>MedicationAdministration.dosage.site.coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>MedicationAdministration.dosage.site.text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
-  </si>
-  <si>
-    <t>C*E.9. But note many systems use C*E.2 for this</t>
   </si>
   <si>
     <t>MedicationAdministration.dosage.route</t>
@@ -1594,11 +1540,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO52"/>
+  <dimension ref="A1:AO48"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="58.58203125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="48.20703125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="55.21875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="45.91796875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.77734375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.8125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.29296875" customWidth="true" bestFit="true"/>
@@ -5600,7 +5546,7 @@
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>134</v>
+        <v>79</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5622,14 +5568,12 @@
         <v>135</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>136</v>
+        <v>309</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>79</v>
@@ -5666,16 +5610,14 @@
         <v>79</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC35" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="AC35" s="2"/>
       <c r="AD35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>79</v>
+        <v>312</v>
       </c>
       <c r="AF35" t="s" s="2">
         <v>246</v>
@@ -5696,7 +5638,7 @@
         <v>79</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>243</v>
+        <v>79</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>79</v>
@@ -5708,48 +5650,46 @@
         <v>79</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="C36" s="2"/>
+        <v>308</v>
+      </c>
+      <c r="C36" t="s" s="2">
+        <v>314</v>
+      </c>
       <c r="D36" t="s" s="2">
-        <v>248</v>
+        <v>79</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>135</v>
+        <v>315</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>249</v>
+        <v>316</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>317</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>79</v>
       </c>
@@ -5797,7 +5737,7 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -5806,7 +5746,7 @@
         <v>81</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>79</v>
+        <v>318</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>140</v>
@@ -5815,7 +5755,7 @@
         <v>79</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>132</v>
+        <v>79</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>79</v>
@@ -5829,10 +5769,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5858,10 +5798,10 @@
         <v>239</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>311</v>
+        <v>240</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>312</v>
+        <v>241</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5912,7 +5852,7 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>310</v>
+        <v>242</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -5924,13 +5864,13 @@
         <v>79</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>313</v>
+        <v>243</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>79</v>
@@ -5942,12 +5882,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5958,10 +5898,10 @@
         <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>79</v>
@@ -5970,17 +5910,15 @@
         <v>79</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>177</v>
+        <v>135</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>317</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>79</v>
@@ -6005,55 +5943,55 @@
         <v>79</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>180</v>
+        <v>79</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>318</v>
+        <v>79</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>319</v>
+        <v>79</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>79</v>
+        <v>311</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>79</v>
+        <v>323</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>79</v>
+        <v>312</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>314</v>
+        <v>246</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>320</v>
+        <v>79</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>321</v>
+        <v>79</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>79</v>
@@ -6061,10 +5999,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6072,7 +6010,7 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>89</v>
@@ -6087,22 +6025,24 @@
         <v>79</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>239</v>
+        <v>103</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>240</v>
+        <v>326</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>327</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>328</v>
+      </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q39" s="2"/>
       <c r="R39" t="s" s="2">
-        <v>79</v>
+        <v>329</v>
       </c>
       <c r="S39" t="s" s="2">
         <v>79</v>
@@ -6144,10 +6084,10 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>242</v>
+        <v>330</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>89</v>
@@ -6162,7 +6102,7 @@
         <v>79</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>243</v>
+        <v>132</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>79</v>
@@ -6176,21 +6116,21 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>134</v>
+        <v>79</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>79</v>
@@ -6202,17 +6142,15 @@
         <v>79</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>135</v>
+        <v>333</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>136</v>
+        <v>334</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>335</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>79</v>
@@ -6249,37 +6187,37 @@
         <v>79</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>324</v>
+        <v>79</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>325</v>
+        <v>79</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>326</v>
+        <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>246</v>
+        <v>336</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>243</v>
+        <v>132</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>79</v>
@@ -6291,46 +6229,48 @@
         <v>79</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="C41" t="s" s="2">
-        <v>328</v>
-      </c>
+        <v>337</v>
+      </c>
+      <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>79</v>
+        <v>248</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I41" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="I41" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="J41" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>329</v>
+        <v>135</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>330</v>
+        <v>249</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
+        <v>250</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>79</v>
       </c>
@@ -6378,7 +6318,7 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6396,7 +6336,7 @@
         <v>79</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>79</v>
+        <v>132</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>79</v>
@@ -6410,10 +6350,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6439,10 +6379,10 @@
         <v>239</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>240</v>
+        <v>339</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>241</v>
+        <v>340</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6493,7 +6433,7 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>242</v>
+        <v>338</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6505,13 +6445,13 @@
         <v>79</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>243</v>
+        <v>341</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>79</v>
@@ -6523,12 +6463,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6539,10 +6479,10 @@
         <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>79</v>
@@ -6551,15 +6491,17 @@
         <v>79</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>135</v>
+        <v>177</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>344</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>345</v>
+      </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>79</v>
@@ -6584,66 +6526,66 @@
         <v>79</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>79</v>
+        <v>180</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>79</v>
+        <v>346</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>79</v>
+        <v>347</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>324</v>
+        <v>79</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>325</v>
+        <v>79</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>326</v>
+        <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>246</v>
+        <v>342</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>79</v>
+        <v>348</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>79</v>
+        <v>349</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>339</v>
+        <v>350</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6657,7 +6599,7 @@
         <v>89</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>79</v>
@@ -6666,24 +6608,22 @@
         <v>79</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>103</v>
+        <v>177</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>340</v>
+        <v>351</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>342</v>
-      </c>
+        <v>352</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q44" s="2"/>
       <c r="R44" t="s" s="2">
-        <v>343</v>
+        <v>79</v>
       </c>
       <c r="S44" t="s" s="2">
         <v>79</v>
@@ -6701,13 +6641,13 @@
         <v>79</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>79</v>
+        <v>180</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>79</v>
+        <v>353</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>79</v>
+        <v>354</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>79</v>
@@ -6725,10 +6665,10 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
         <v>89</v>
@@ -6737,19 +6677,19 @@
         <v>79</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>132</v>
+        <v>355</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>79</v>
+        <v>356</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>79</v>
@@ -6757,10 +6697,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>345</v>
+        <v>357</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>346</v>
+        <v>357</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6768,7 +6708,7 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>89</v>
@@ -6783,15 +6723,17 @@
         <v>79</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>347</v>
+        <v>177</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>348</v>
+        <v>358</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>359</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>360</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>79</v>
@@ -6816,13 +6758,13 @@
         <v>79</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>79</v>
+        <v>180</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>79</v>
+        <v>361</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>79</v>
+        <v>362</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>79</v>
@@ -6840,7 +6782,7 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -6858,24 +6800,24 @@
         <v>79</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>132</v>
+        <v>363</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>79</v>
+        <v>364</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
-        <v>351</v>
+        <v>365</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>351</v>
+        <v>365</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6883,35 +6825,33 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>352</v>
+        <v>366</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>353</v>
+        <v>367</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>354</v>
+        <v>368</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>356</v>
-      </c>
+        <v>369</v>
+      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>79</v>
       </c>
@@ -6959,13 +6899,13 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>79</v>
@@ -6977,13 +6917,13 @@
         <v>79</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>358</v>
+        <v>370</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>79</v>
@@ -6991,10 +6931,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>360</v>
+        <v>372</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>360</v>
+        <v>372</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7014,23 +6954,21 @@
         <v>79</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>239</v>
+        <v>373</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>361</v>
+        <v>374</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>362</v>
+        <v>375</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>364</v>
-      </c>
+        <v>376</v>
+      </c>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>79</v>
       </c>
@@ -7078,7 +7016,7 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7096,24 +7034,24 @@
         <v>79</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>367</v>
+        <v>378</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7121,13 +7059,13 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>79</v>
@@ -7136,15 +7074,17 @@
         <v>79</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>177</v>
+        <v>380</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>382</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>383</v>
+      </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>79</v>
@@ -7169,13 +7109,13 @@
         <v>79</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>180</v>
+        <v>79</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>371</v>
+        <v>79</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>372</v>
+        <v>79</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>79</v>
@@ -7193,13 +7133,13 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>79</v>
@@ -7211,488 +7151,20 @@
         <v>79</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>374</v>
+        <v>79</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="49" hidden="true">
-      <c r="A49" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="B49" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="C49" s="2"/>
-      <c r="D49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E49" s="2"/>
-      <c r="F49" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G49" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K49" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="L49" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="O49" s="2"/>
-      <c r="P49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q49" s="2"/>
-      <c r="R49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X49" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="Y49" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="Z49" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="AA49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF49" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="AG49" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH49" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ49" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL49" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="AO49" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="B50" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="C50" s="2"/>
-      <c r="D50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E50" s="2"/>
-      <c r="F50" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="G50" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H50" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="I50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K50" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="L50" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="O50" s="2"/>
-      <c r="P50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q50" s="2"/>
-      <c r="R50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF50" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="AG50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH50" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ50" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL50" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="AO50" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="51" hidden="true">
-      <c r="A51" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="B51" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="C51" s="2"/>
-      <c r="D51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E51" s="2"/>
-      <c r="F51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G51" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K51" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="L51" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="O51" s="2"/>
-      <c r="P51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q51" s="2"/>
-      <c r="R51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF51" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="AG51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH51" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ51" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL51" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="AO51" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="52" hidden="true">
-      <c r="A52" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="B52" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="C52" s="2"/>
-      <c r="D52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E52" s="2"/>
-      <c r="F52" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G52" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K52" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="L52" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="O52" s="2"/>
-      <c r="P52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q52" s="2"/>
-      <c r="R52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="AG52" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH52" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ52" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL52" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="AM52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO52" t="s" s="2">
         <v>79</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO52">
+  <autoFilter ref="A1:AO48">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -7702,7 +7174,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI51">
+  <conditionalFormatting sqref="A2:AI47">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
